--- a/results/bets_placed.xlsx
+++ b/results/bets_placed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>date</t>
   </si>
@@ -87,12 +87,31 @@
   <si>
     <t>actual_profit_loss</t>
   </si>
+  <si>
+    <t>ROI</t>
+  </si>
+  <si>
+    <t>balance</t>
+  </si>
+  <si>
+    <t>ROC</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,15 +137,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -428,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:U500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -436,106 +458,87 @@
     <col min="12" max="12" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O1">
+        <f>SUM(O3:O900)</f>
+        <v>457</v>
+      </c>
+      <c r="P1">
+        <f>SUM(P3:P900)</f>
+        <v>84.430000000000035</v>
+      </c>
+      <c r="Q1">
+        <f>Q500</f>
+        <v>2084.4300000000003</v>
+      </c>
+      <c r="R1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="2">
+        <f>P1/O1</f>
+        <v>0.1847483588621445</v>
+      </c>
+      <c r="T1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="2">
+        <f>Q1/Q3-1</f>
+        <v>4.2215000000000114E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O2" t="s">
         <v>22</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="Q2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>9186</v>
-      </c>
-      <c r="B2" s="1">
-        <v>45689</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>1.3448275862068899</v>
-      </c>
-      <c r="G2">
-        <v>3.5</v>
-      </c>
-      <c r="H2">
-        <v>77.5</v>
-      </c>
-      <c r="I2">
-        <v>21.1</v>
-      </c>
-      <c r="J2">
-        <v>0.04</v>
-      </c>
-      <c r="K2">
-        <v>-0.26</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2">
-        <v>112.117233872413</v>
-      </c>
-      <c r="N2">
-        <v>38.661115128418402</v>
-      </c>
-      <c r="O2">
-        <v>112</v>
-      </c>
-      <c r="P2">
-        <v>37.330000000000013</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>9188</v>
       </c>
       <c r="B3" s="1">
         <v>45689</v>
@@ -544,48 +547,51 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>1.625</v>
+        <v>1.3448275862068899</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="H3">
-        <v>68</v>
+        <v>77.5</v>
       </c>
       <c r="I3">
-        <v>30.4</v>
+        <v>21.1</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="K3">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="L3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>116.754641532897</v>
+        <v>112.117233872413</v>
       </c>
       <c r="N3">
-        <v>72.971650958061204</v>
+        <v>38.661115128418402</v>
       </c>
       <c r="O3">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="P3">
-        <v>-116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>37.330000000000013</v>
+      </c>
+      <c r="Q3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>9189</v>
+        <v>9188</v>
       </c>
       <c r="B4" s="1">
         <v>45689</v>
@@ -594,48 +600,52 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>2.21999999999999</v>
+        <v>1.625</v>
       </c>
       <c r="G4">
-        <v>1.74074074074074</v>
+        <v>2.5</v>
       </c>
       <c r="H4">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I4">
-        <v>43.3</v>
+        <v>30.4</v>
       </c>
       <c r="J4">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="K4">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="L4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M4">
-        <v>118.15781524923899</v>
+        <v>116.754641532897</v>
       </c>
       <c r="N4">
-        <v>144.152534604072</v>
+        <v>72.971650958061204</v>
       </c>
       <c r="O4">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P4">
-        <v>129.80000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-116</v>
+      </c>
+      <c r="Q4">
+        <f>Q3+P3</f>
+        <v>2037.33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>9191</v>
+        <v>9189</v>
       </c>
       <c r="B5" s="1">
         <v>45689</v>
@@ -644,43 +654,3065 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>2.21999999999999</v>
+      </c>
+      <c r="G5">
+        <v>1.74074074074074</v>
+      </c>
+      <c r="H5">
+        <v>55</v>
+      </c>
+      <c r="I5">
+        <v>43.3</v>
+      </c>
+      <c r="J5">
+        <v>0.22</v>
+      </c>
+      <c r="K5">
+        <v>-0.25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5">
+        <v>118.15781524923899</v>
+      </c>
+      <c r="N5">
+        <v>144.152534604072</v>
+      </c>
+      <c r="O5">
+        <v>118</v>
+      </c>
+      <c r="P5">
+        <v>129.80000000000001</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q68" si="0">Q4+P4</f>
+        <v>1921.33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>9191</v>
+      </c>
+      <c r="B6" s="1">
+        <v>45689</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>1.3076923076922999</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>3.8</v>
       </c>
-      <c r="H5">
+      <c r="H6">
         <v>79.099999999999994</v>
       </c>
-      <c r="I5">
+      <c r="I6">
         <v>19.5</v>
       </c>
-      <c r="J5">
+      <c r="J6">
         <v>0.03</v>
       </c>
-      <c r="K5">
+      <c r="K6">
         <v>-0.26</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L6" t="s">
         <v>20</v>
       </c>
-      <c r="M5">
+      <c r="M6">
         <v>111.27161979675201</v>
       </c>
-      <c r="N5">
+      <c r="N6">
         <v>34.237421475923902</v>
       </c>
-      <c r="O5">
+      <c r="O6">
         <v>111</v>
       </c>
-      <c r="P5">
+      <c r="P6">
         <v>33.300000000000011</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>2051.13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q16">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q17">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q18">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q19">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q20">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q21">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q22">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q23">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q24">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q25">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q26">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q27">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q28">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q29">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="30" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q30">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q31">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q32">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q33">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q34">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q35">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q36">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q37">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q38">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q39">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q40">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q41">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q42">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q43">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="44" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q44">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q45">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="46" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q46">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q47">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="48" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q48">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q49">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q50">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="51" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q51">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="52" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q52">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q53">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="54" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q54">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q55">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q56">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="57" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q57">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="58" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q58">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="59" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q59">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q60">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q61">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q62">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q63">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q64">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q65">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q66">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q67">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q68">
+        <f t="shared" si="0"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="69" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q69">
+        <f t="shared" ref="Q69:Q132" si="1">Q68+P68</f>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q70">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="71" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q71">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="72" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q72">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="73" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q73">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="74" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q74">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="75" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q75">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q76">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="77" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q77">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="78" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q78">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q79">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q80">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="81" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q81">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q82">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="83" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q83">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="84" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q84">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="85" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q85">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="86" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q86">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="87" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q87">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="88" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q88">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q89">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="90" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q90">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q91">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q92">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="93" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q93">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="94" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q94">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="95" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q95">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="96" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q96">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="97" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q97">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="98" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q98">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="99" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q99">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="100" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q100">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="101" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q101">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="102" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q102">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="103" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q103">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="104" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q104">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="105" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q105">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="106" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q106">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="107" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q107">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="108" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q108">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="109" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q109">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="110" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q110">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="111" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q111">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="112" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q112">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="113" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q113">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="114" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q114">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="115" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q115">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="116" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q116">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="117" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q117">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="118" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q118">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q119">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="120" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q120">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="121" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q121">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="122" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q122">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="123" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q123">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="124" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q124">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="125" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q125">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="126" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q126">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="127" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q127">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="128" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q128">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="129" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q129">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="130" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q130">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="131" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q131">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="132" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q132">
+        <f t="shared" si="1"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="133" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q133">
+        <f t="shared" ref="Q133:Q196" si="2">Q132+P132</f>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="134" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q134">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="135" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q135">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="136" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q136">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="137" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q137">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="138" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q138">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="139" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q139">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="140" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q140">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="141" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q141">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="142" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q142">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="143" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q143">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="144" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q144">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="145" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q145">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="146" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q146">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="147" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q147">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="148" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q148">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="149" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q149">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="150" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q150">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="151" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q151">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="152" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q152">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="153" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q153">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="154" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q154">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="155" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q155">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="156" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q156">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="157" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q157">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="158" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q158">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="159" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q159">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="160" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q160">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="161" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q161">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="162" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q162">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="163" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q163">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="164" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q164">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="165" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q165">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="166" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q166">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="167" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q167">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="168" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q168">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="169" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q169">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="170" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q170">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="171" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q171">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="172" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q172">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="173" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q173">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="174" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q174">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="175" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q175">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="176" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q176">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="177" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q177">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="178" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q178">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="179" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q179">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="180" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q180">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="181" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q181">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="182" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q182">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="183" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q183">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="184" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q184">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="185" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q185">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="186" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q186">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="187" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q187">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="188" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q188">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="189" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q189">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="190" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q190">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="191" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q191">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="192" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q192">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="193" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q193">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="194" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q194">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="195" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q195">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="196" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q196">
+        <f t="shared" si="2"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="197" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q197">
+        <f t="shared" ref="Q197:Q260" si="3">Q196+P196</f>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="198" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q198">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="199" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q199">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="200" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q200">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="201" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q201">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="202" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q202">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="203" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q203">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="204" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q204">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="205" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q205">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="206" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q206">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="207" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q207">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="208" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q208">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="209" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q209">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="210" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q210">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="211" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q211">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="212" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q212">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="213" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q213">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="214" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q214">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="215" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q215">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="216" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q216">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="217" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q217">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="218" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q218">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="219" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q219">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="220" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q220">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="221" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q221">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="222" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q222">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="223" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q223">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="224" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q224">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="225" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q225">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="226" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q226">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="227" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q227">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="228" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q228">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="229" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q229">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="230" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q230">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="231" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q231">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="232" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q232">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="233" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q233">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="234" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q234">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="235" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q235">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="236" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q236">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="237" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q237">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="238" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q238">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="239" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q239">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="240" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q240">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="241" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q241">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="242" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q242">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="243" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q243">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="244" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q244">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="245" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q245">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="246" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q246">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="247" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q247">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="248" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q248">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="249" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q249">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="250" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q250">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="251" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q251">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="252" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q252">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="253" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q253">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="254" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q254">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="255" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q255">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="256" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q256">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="257" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q257">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="258" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q258">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="259" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q259">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="260" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q260">
+        <f t="shared" si="3"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="261" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q261">
+        <f t="shared" ref="Q261:Q324" si="4">Q260+P260</f>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="262" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q262">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="263" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q263">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="264" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q264">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="265" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q265">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="266" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q266">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="267" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q267">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="268" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q268">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="269" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q269">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="270" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q270">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="271" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q271">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="272" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q272">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="273" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q273">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="274" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q274">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="275" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q275">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="276" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q276">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="277" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q277">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="278" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q278">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="279" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q279">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="280" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q280">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="281" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q281">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="282" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q282">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="283" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q283">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="284" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q284">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="285" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q285">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="286" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q286">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="287" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q287">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="288" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q288">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="289" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q289">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="290" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q290">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="291" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q291">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="292" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q292">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="293" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q293">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="294" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q294">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="295" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q295">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="296" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q296">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="297" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q297">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="298" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q298">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="299" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q299">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="300" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q300">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="301" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q301">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="302" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q302">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="303" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q303">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="304" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q304">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="305" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q305">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="306" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q306">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="307" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q307">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="308" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q308">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="309" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q309">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="310" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q310">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="311" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q311">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="312" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q312">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="313" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q313">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="314" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q314">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="315" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q315">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="316" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q316">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="317" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q317">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="318" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q318">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="319" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q319">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="320" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q320">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="321" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q321">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="322" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q322">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="323" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q323">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="324" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q324">
+        <f t="shared" si="4"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="325" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q325">
+        <f t="shared" ref="Q325:Q388" si="5">Q324+P324</f>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="326" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q326">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="327" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q327">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="328" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q328">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="329" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q329">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="330" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q330">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="331" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q331">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="332" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q332">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="333" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q333">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="334" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q334">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="335" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q335">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="336" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q336">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="337" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q337">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="338" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q338">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="339" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q339">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="340" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q340">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="341" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q341">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="342" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q342">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="343" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q343">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="344" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q344">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="345" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q345">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="346" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q346">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="347" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q347">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="348" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q348">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="349" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q349">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="350" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q350">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="351" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q351">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="352" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q352">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="353" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q353">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="354" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q354">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="355" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q355">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="356" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q356">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="357" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q357">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="358" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q358">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="359" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q359">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="360" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q360">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="361" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q361">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="362" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q362">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="363" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q363">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="364" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q364">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="365" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q365">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="366" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q366">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="367" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q367">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="368" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q368">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="369" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q369">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="370" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q370">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="371" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q371">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="372" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q372">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="373" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q373">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="374" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q374">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="375" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q375">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="376" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q376">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="377" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q377">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="378" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q378">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="379" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q379">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="380" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q380">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="381" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q381">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="382" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q382">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="383" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q383">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="384" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q384">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="385" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q385">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="386" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q386">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="387" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q387">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="388" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q388">
+        <f t="shared" si="5"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="389" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q389">
+        <f t="shared" ref="Q389:Q452" si="6">Q388+P388</f>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="390" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q390">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="391" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q391">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="392" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q392">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="393" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q393">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="394" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q394">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="395" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q395">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="396" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q396">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="397" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q397">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="398" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q398">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="399" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q399">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="400" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q400">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="401" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q401">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="402" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q402">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="403" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q403">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="404" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q404">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="405" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q405">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="406" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q406">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="407" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q407">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="408" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q408">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="409" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q409">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="410" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q410">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="411" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q411">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="412" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q412">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="413" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q413">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="414" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q414">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="415" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q415">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="416" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q416">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="417" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q417">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="418" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q418">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="419" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q419">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="420" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q420">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="421" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q421">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="422" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q422">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="423" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q423">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="424" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q424">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="425" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q425">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="426" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q426">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="427" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q427">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="428" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q428">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="429" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q429">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="430" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q430">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="431" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q431">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="432" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q432">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="433" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q433">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="434" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q434">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="435" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q435">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="436" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q436">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="437" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q437">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="438" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q438">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="439" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q439">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="440" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q440">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="441" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q441">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="442" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q442">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="443" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q443">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="444" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q444">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="445" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q445">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="446" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q446">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="447" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q447">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="448" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q448">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="449" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q449">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="450" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q450">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="451" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q451">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="452" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q452">
+        <f t="shared" si="6"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="453" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q453">
+        <f t="shared" ref="Q453:Q516" si="7">Q452+P452</f>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="454" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q454">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="455" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q455">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="456" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q456">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="457" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q457">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="458" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q458">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="459" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q459">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="460" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q460">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="461" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q461">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="462" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q462">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="463" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q463">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="464" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q464">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="465" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q465">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="466" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q466">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="467" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q467">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="468" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q468">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="469" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q469">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="470" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q470">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="471" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q471">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="472" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q472">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="473" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q473">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="474" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q474">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="475" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q475">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="476" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q476">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="477" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q477">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="478" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q478">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="479" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q479">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="480" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q480">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="481" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q481">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="482" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q482">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="483" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q483">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="484" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q484">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="485" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q485">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="486" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q486">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="487" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q487">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="488" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q488">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="489" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q489">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="490" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q490">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="491" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q491">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="492" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q492">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="493" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q493">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="494" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q494">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="495" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q495">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="496" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q496">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="497" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q497">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="498" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q498">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="499" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q499">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
+      </c>
+    </row>
+    <row r="500" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q500">
+        <f t="shared" si="7"/>
+        <v>2084.4300000000003</v>
       </c>
     </row>
   </sheetData>

--- a/results/bets_placed.xlsx
+++ b/results/bets_placed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>date</t>
   </si>
@@ -122,6 +122,15 @@
   </si>
   <si>
     <t>CAGR</t>
+  </si>
+  <si>
+    <t>ufcfightnight:cannoniervsrodrigues</t>
+  </si>
+  <si>
+    <t>gabrielbonfim</t>
+  </si>
+  <si>
+    <t>khaoswilliams</t>
   </si>
 </sst>
 </file>
@@ -492,36 +501,36 @@
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="O1">
         <f>SUM(O3:O900)</f>
-        <v>825</v>
+        <v>955</v>
       </c>
       <c r="Q1">
         <f>SUM(Q3:Q900)</f>
-        <v>132.98000000000002</v>
+        <v>197.98000000000002</v>
       </c>
       <c r="R1">
         <f>R500</f>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
       <c r="S1" t="s">
         <v>24</v>
       </c>
       <c r="T1" s="2">
         <f>Q1/O1</f>
-        <v>0.1611878787878788</v>
+        <v>0.20730890052356024</v>
       </c>
       <c r="U1" t="s">
         <v>26</v>
       </c>
       <c r="V1" s="2">
         <f>R1/R3-1</f>
-        <v>6.649000000000016E-2</v>
+        <v>9.8990000000000133E-2</v>
       </c>
       <c r="X1" t="s">
         <v>35</v>
       </c>
       <c r="Y1" s="4">
         <f ca="1">(1+V1)^(1/(X2-B3))^365-1</f>
-        <v>17.859424462272457</v>
+        <v>8.9429294199783769</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
@@ -578,7 +587,7 @@
       </c>
       <c r="X2" s="1">
         <f ca="1">TODAY()</f>
-        <v>45697</v>
+        <v>45704</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -969,6 +978,57 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9215</v>
+      </c>
+      <c r="B10" s="1">
+        <v>45703</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10">
+        <v>1.48780487804878</v>
+      </c>
+      <c r="G10">
+        <v>2.85</v>
+      </c>
+      <c r="H10">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="I10">
+        <v>28.5</v>
+      </c>
+      <c r="J10">
+        <v>0.04</v>
+      </c>
+      <c r="K10">
+        <v>-0.19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <v>127.978799999999</v>
+      </c>
+      <c r="N10">
+        <v>62.428682926829197</v>
+      </c>
+      <c r="O10">
+        <v>130</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="Q10">
+        <v>65</v>
+      </c>
       <c r="R10">
         <f t="shared" si="0"/>
         <v>2132.9800000000005</v>
@@ -978,2941 +1038,2941 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R11">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R12">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R13">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R14">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R15">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R16">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="17" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R17">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="18" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R18">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="19" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R19">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="20" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R20">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="21" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R21">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="22" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R22">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="23" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R23">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="24" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R24">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="25" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R25">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="26" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R26">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="27" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R27">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="28" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R28">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="29" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R29">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="30" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R30">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="31" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R31">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="32" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R32">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="33" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R33">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="34" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R34">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="35" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R35">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="36" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R36">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="37" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R37">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="38" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R38">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="39" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R39">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="40" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R40">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="41" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R41">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="42" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R42">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="43" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R43">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="44" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R44">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="45" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R45">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="46" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R46">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="47" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R47">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="48" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R48">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="49" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R49">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="50" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R50">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="51" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R51">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="52" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R52">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="53" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R53">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="54" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R54">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="55" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R55">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="56" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R56">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="57" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R57">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="58" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R58">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="59" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R59">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="60" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R60">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="61" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R61">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="62" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R62">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="63" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R63">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="64" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R64">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="65" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R65">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="66" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R66">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="67" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R67">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="68" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R68">
         <f t="shared" si="0"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="69" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R69">
         <f t="shared" ref="R69:R132" si="1">R68+Q68</f>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="70" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R70">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="71" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R71">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="72" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R72">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="73" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R73">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="74" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R74">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="75" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R75">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="76" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R76">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="77" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R77">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="78" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R78">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="79" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R79">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="80" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R80">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="81" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R81">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="82" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R82">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="83" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R83">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="84" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R84">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="85" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R85">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="86" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R86">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="87" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R87">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="88" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R88">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="89" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R89">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="90" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R90">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="91" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R91">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="92" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R92">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="93" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R93">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="94" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R94">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="95" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R95">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="96" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R96">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="97" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R97">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="98" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R98">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="99" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R99">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="100" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R100">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="101" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R101">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="102" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R102">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="103" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R103">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="104" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R104">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="105" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R105">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="106" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R106">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="107" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R107">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="108" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R108">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="109" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R109">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="110" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R110">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="111" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R111">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="112" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R112">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="113" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R113">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="114" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R114">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="115" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R115">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="116" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R116">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="117" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R117">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="118" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R118">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="119" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R119">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="120" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R120">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="121" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R121">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="122" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R122">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="123" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R123">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="124" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R124">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="125" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R125">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="126" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R126">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="127" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R127">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="128" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R128">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="129" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R129">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="130" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R130">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="131" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R131">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="132" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R132">
         <f t="shared" si="1"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="133" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R133">
         <f t="shared" ref="R133:R196" si="2">R132+Q132</f>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="134" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R134">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="135" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R135">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="136" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R136">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="137" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R137">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="138" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R138">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="139" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R139">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="140" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R140">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="141" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R141">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="142" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R142">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="143" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R143">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="144" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R144">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="145" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R145">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="146" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R146">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="147" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R147">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="148" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R148">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="149" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R149">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="150" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R150">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="151" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R151">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="152" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R152">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="153" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R153">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="154" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R154">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="155" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R155">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="156" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R156">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="157" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R157">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="158" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R158">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="159" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R159">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="160" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R160">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="161" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R161">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="162" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R162">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="163" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R163">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="164" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R164">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="165" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R165">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="166" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R166">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="167" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R167">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="168" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R168">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="169" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R169">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="170" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R170">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="171" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R171">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="172" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R172">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="173" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R173">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="174" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R174">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="175" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R175">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="176" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R176">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="177" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R177">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="178" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R178">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="179" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R179">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="180" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R180">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="181" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R181">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="182" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R182">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="183" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R183">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="184" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R184">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="185" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R185">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="186" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R186">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="187" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R187">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="188" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R188">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="189" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R189">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="190" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R190">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="191" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R191">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="192" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R192">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="193" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R193">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="194" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R194">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="195" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R195">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="196" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R196">
         <f t="shared" si="2"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="197" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R197">
         <f t="shared" ref="R197:R260" si="3">R196+Q196</f>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="198" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R198">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="199" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R199">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="200" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R200">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="201" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R201">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="202" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R202">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="203" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R203">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="204" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R204">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="205" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R205">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="206" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R206">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="207" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R207">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="208" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R208">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="209" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R209">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="210" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R210">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="211" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R211">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="212" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R212">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="213" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R213">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="214" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R214">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="215" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R215">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="216" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R216">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="217" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R217">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="218" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R218">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="219" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R219">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="220" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R220">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="221" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R221">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="222" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R222">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="223" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R223">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="224" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R224">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="225" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R225">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="226" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R226">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="227" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R227">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="228" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R228">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="229" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R229">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="230" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R230">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="231" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R231">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="232" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R232">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="233" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R233">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="234" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R234">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="235" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R235">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="236" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R236">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="237" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R237">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="238" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R238">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="239" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R239">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="240" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R240">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="241" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R241">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="242" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R242">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="243" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R243">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="244" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R244">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="245" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R245">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="246" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R246">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="247" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R247">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="248" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R248">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="249" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R249">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="250" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R250">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="251" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R251">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="252" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R252">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="253" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R253">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="254" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R254">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="255" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R255">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="256" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R256">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="257" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R257">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="258" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R258">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="259" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R259">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="260" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R260">
         <f t="shared" si="3"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="261" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R261">
         <f t="shared" ref="R261:R324" si="4">R260+Q260</f>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="262" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R262">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="263" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R263">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="264" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R264">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="265" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R265">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="266" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R266">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="267" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R267">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="268" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R268">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="269" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R269">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="270" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R270">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="271" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R271">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="272" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R272">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="273" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R273">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="274" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R274">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="275" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R275">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="276" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R276">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="277" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R277">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="278" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R278">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="279" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R279">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="280" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R280">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="281" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R281">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="282" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R282">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="283" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R283">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="284" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R284">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="285" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R285">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="286" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R286">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="287" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R287">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="288" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R288">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="289" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R289">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="290" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R290">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="291" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R291">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="292" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R292">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="293" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R293">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="294" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R294">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="295" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R295">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="296" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R296">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="297" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R297">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="298" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R298">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="299" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R299">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="300" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R300">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="301" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R301">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="302" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R302">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="303" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R303">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="304" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R304">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="305" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R305">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="306" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R306">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="307" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R307">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="308" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R308">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="309" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R309">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="310" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R310">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="311" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R311">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="312" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R312">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="313" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R313">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="314" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R314">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="315" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R315">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="316" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R316">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="317" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R317">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="318" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R318">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="319" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R319">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="320" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R320">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="321" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R321">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="322" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R322">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="323" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R323">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="324" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R324">
         <f t="shared" si="4"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="325" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R325">
         <f t="shared" ref="R325:R388" si="5">R324+Q324</f>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="326" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R326">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="327" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R327">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="328" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R328">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="329" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R329">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="330" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R330">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="331" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R331">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="332" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R332">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="333" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R333">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="334" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R334">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="335" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R335">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="336" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R336">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="337" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R337">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="338" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R338">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="339" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R339">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="340" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R340">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="341" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R341">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="342" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R342">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="343" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R343">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="344" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R344">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="345" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R345">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="346" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R346">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="347" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R347">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="348" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R348">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="349" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R349">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="350" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R350">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="351" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R351">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="352" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R352">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="353" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R353">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="354" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R354">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="355" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R355">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="356" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R356">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="357" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R357">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="358" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R358">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="359" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R359">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="360" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R360">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="361" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R361">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="362" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R362">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="363" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R363">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="364" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R364">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="365" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R365">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="366" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R366">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="367" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R367">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="368" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R368">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="369" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R369">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="370" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R370">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="371" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R371">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="372" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R372">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="373" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R373">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="374" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R374">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="375" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R375">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="376" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R376">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="377" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R377">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="378" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R378">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="379" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R379">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="380" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R380">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="381" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R381">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="382" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R382">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="383" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R383">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="384" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R384">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="385" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R385">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="386" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R386">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="387" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R387">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="388" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R388">
         <f t="shared" si="5"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="389" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R389">
         <f t="shared" ref="R389:R452" si="6">R388+Q388</f>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="390" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R390">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="391" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R391">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="392" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R392">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="393" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R393">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="394" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R394">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="395" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R395">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="396" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R396">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="397" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R397">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="398" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R398">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="399" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R399">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="400" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R400">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="401" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R401">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="402" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R402">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="403" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R403">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="404" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R404">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="405" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R405">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="406" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R406">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="407" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R407">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="408" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R408">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="409" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R409">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="410" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R410">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="411" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R411">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="412" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R412">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="413" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R413">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="414" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R414">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="415" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R415">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="416" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R416">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="417" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R417">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="418" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R418">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="419" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R419">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="420" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R420">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="421" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R421">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="422" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R422">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="423" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R423">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="424" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R424">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="425" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R425">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="426" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R426">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="427" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R427">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="428" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R428">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="429" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R429">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="430" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R430">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="431" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R431">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="432" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R432">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="433" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R433">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="434" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R434">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="435" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R435">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="436" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R436">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="437" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R437">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="438" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R438">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="439" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R439">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="440" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R440">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="441" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R441">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="442" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R442">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="443" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R443">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="444" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R444">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="445" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R445">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="446" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R446">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="447" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R447">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="448" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R448">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="449" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R449">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="450" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R450">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="451" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R451">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="452" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R452">
         <f t="shared" si="6"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="453" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R453">
         <f t="shared" ref="R453:R500" si="7">R452+Q452</f>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="454" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R454">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="455" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R455">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="456" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R456">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="457" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R457">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="458" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R458">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="459" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R459">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="460" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R460">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="461" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R461">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="462" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R462">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="463" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R463">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="464" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R464">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="465" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R465">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="466" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R466">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="467" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R467">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="468" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R468">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="469" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R469">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="470" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R470">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="471" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R471">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="472" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R472">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="473" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R473">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="474" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R474">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="475" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R475">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="476" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R476">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="477" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R477">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="478" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R478">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="479" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R479">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="480" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R480">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="481" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R481">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="482" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R482">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="483" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R483">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="484" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R484">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="485" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R485">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="486" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R486">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="487" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R487">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="488" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R488">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="489" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R489">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="490" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R490">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="491" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R491">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="492" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R492">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="493" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R493">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="494" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R494">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="495" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R495">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="496" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R496">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="497" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R497">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="498" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R498">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="499" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R499">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
     <row r="500" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R500">
         <f t="shared" si="7"/>
-        <v>2132.9800000000005</v>
+        <v>2197.9800000000005</v>
       </c>
     </row>
   </sheetData>
